--- a/question_data_cleaned.xlsx
+++ b/question_data_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q179"/>
+  <dimension ref="A1:R179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,47 +471,52 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>answer_type</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>meta_data</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ordinal</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>is_reset_question</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Eng checked</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>questionnaire_group_question_id</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>questionnaire_group_version_id</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>default_answer_if_hidden</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>answer_type</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>meta_data</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>group_name</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>ordinal</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>is_reset_question</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Eng checked</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>questionnaire_group_question_id</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>questionnaire_group_version_id</t>
         </is>
       </c>
     </row>
@@ -591,6 +596,7 @@
       <c r="Q2" t="n">
         <v>1</v>
       </c>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -668,6 +674,7 @@
       <c r="Q3" t="n">
         <v>1</v>
       </c>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -745,6 +752,7 @@
       <c r="Q4" t="n">
         <v>2</v>
       </c>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -822,6 +830,7 @@
       <c r="Q5" t="n">
         <v>2</v>
       </c>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -899,6 +908,7 @@
       <c r="Q6" t="n">
         <v>2</v>
       </c>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -976,6 +986,7 @@
       <c r="Q7" t="n">
         <v>2</v>
       </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1053,6 +1064,7 @@
       <c r="Q8" t="n">
         <v>2</v>
       </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1130,6 +1142,7 @@
       <c r="Q9" t="n">
         <v>2</v>
       </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1207,6 +1220,7 @@
       <c r="Q10" t="n">
         <v>2</v>
       </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1284,6 +1298,7 @@
       <c r="Q11" t="n">
         <v>2</v>
       </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1361,6 +1376,7 @@
       <c r="Q12" t="n">
         <v>2</v>
       </c>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1438,6 +1454,7 @@
       <c r="Q13" t="n">
         <v>2</v>
       </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1515,6 +1532,7 @@
       <c r="Q14" t="n">
         <v>2</v>
       </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1592,6 +1610,7 @@
       <c r="Q15" t="n">
         <v>2</v>
       </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1669,6 +1688,7 @@
       <c r="Q16" t="n">
         <v>3</v>
       </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1744,6 +1764,7 @@
       <c r="Q17" t="n">
         <v>3</v>
       </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1819,6 +1840,7 @@
       <c r="Q18" t="n">
         <v>3</v>
       </c>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1894,6 +1916,7 @@
       <c r="Q19" t="n">
         <v>3</v>
       </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1969,6 +1992,7 @@
       <c r="Q20" t="n">
         <v>3</v>
       </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2044,6 +2068,7 @@
       <c r="Q21" t="n">
         <v>3</v>
       </c>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2121,6 +2146,7 @@
       <c r="Q22" t="n">
         <v>4</v>
       </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2198,6 +2224,7 @@
       <c r="Q23" t="n">
         <v>4</v>
       </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2275,6 +2302,7 @@
       <c r="Q24" t="n">
         <v>4</v>
       </c>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2352,6 +2380,7 @@
       <c r="Q25" t="n">
         <v>4</v>
       </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2429,6 +2458,7 @@
       <c r="Q26" t="n">
         <v>4</v>
       </c>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2506,6 +2536,7 @@
       <c r="Q27" t="n">
         <v>4</v>
       </c>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2583,6 +2614,7 @@
       <c r="Q28" t="n">
         <v>4</v>
       </c>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2660,6 +2692,7 @@
       <c r="Q29" t="n">
         <v>4</v>
       </c>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2737,6 +2770,7 @@
       <c r="Q30" t="n">
         <v>4</v>
       </c>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2814,6 +2848,7 @@
       <c r="Q31" t="n">
         <v>4</v>
       </c>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2891,6 +2926,7 @@
       <c r="Q32" t="n">
         <v>4</v>
       </c>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2968,6 +3004,7 @@
       <c r="Q33" t="n">
         <v>4</v>
       </c>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3045,6 +3082,7 @@
       <c r="Q34" t="n">
         <v>4</v>
       </c>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3122,6 +3160,7 @@
       <c r="Q35" t="n">
         <v>4</v>
       </c>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3199,6 +3238,7 @@
       <c r="Q36" t="n">
         <v>4</v>
       </c>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3276,6 +3316,7 @@
       <c r="Q37" t="n">
         <v>4</v>
       </c>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3353,6 +3394,7 @@
       <c r="Q38" t="n">
         <v>5</v>
       </c>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3428,6 +3470,7 @@
       <c r="Q39" t="n">
         <v>5</v>
       </c>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3503,6 +3546,7 @@
       <c r="Q40" t="n">
         <v>5</v>
       </c>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3578,6 +3622,7 @@
       <c r="Q41" t="n">
         <v>5</v>
       </c>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3653,6 +3698,7 @@
       <c r="Q42" t="n">
         <v>5</v>
       </c>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3728,6 +3774,7 @@
       <c r="Q43" t="n">
         <v>5</v>
       </c>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3803,6 +3850,7 @@
       <c r="Q44" t="n">
         <v>5</v>
       </c>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3878,6 +3926,7 @@
       <c r="Q45" t="n">
         <v>5</v>
       </c>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3953,6 +4002,7 @@
       <c r="Q46" t="n">
         <v>5</v>
       </c>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4028,6 +4078,7 @@
       <c r="Q47" t="n">
         <v>5</v>
       </c>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4103,6 +4154,7 @@
       <c r="Q48" t="n">
         <v>5</v>
       </c>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4178,6 +4230,7 @@
       <c r="Q49" t="n">
         <v>5</v>
       </c>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4253,6 +4306,7 @@
       <c r="Q50" t="n">
         <v>5</v>
       </c>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4328,6 +4382,7 @@
       <c r="Q51" t="n">
         <v>5</v>
       </c>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4403,6 +4458,7 @@
       <c r="Q52" t="n">
         <v>5</v>
       </c>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4478,6 +4534,7 @@
       <c r="Q53" t="n">
         <v>5</v>
       </c>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4555,6 +4612,7 @@
       <c r="Q54" t="n">
         <v>5</v>
       </c>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4630,6 +4688,7 @@
       <c r="Q55" t="n">
         <v>5</v>
       </c>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4705,6 +4764,7 @@
       <c r="Q56" t="n">
         <v>5</v>
       </c>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4780,6 +4840,7 @@
       <c r="Q57" t="n">
         <v>5</v>
       </c>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4855,6 +4916,7 @@
       <c r="Q58" t="n">
         <v>5</v>
       </c>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4930,6 +4992,7 @@
       <c r="Q59" t="n">
         <v>5</v>
       </c>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5005,6 +5068,7 @@
       <c r="Q60" t="n">
         <v>5</v>
       </c>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5080,6 +5144,7 @@
       <c r="Q61" t="n">
         <v>5</v>
       </c>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5155,6 +5220,7 @@
       <c r="Q62" t="n">
         <v>5</v>
       </c>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5230,6 +5296,7 @@
       <c r="Q63" t="n">
         <v>5</v>
       </c>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5305,6 +5372,7 @@
       <c r="Q64" t="n">
         <v>5</v>
       </c>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5380,6 +5448,7 @@
       <c r="Q65" t="n">
         <v>5</v>
       </c>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5455,6 +5524,7 @@
       <c r="Q66" t="n">
         <v>5</v>
       </c>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5530,6 +5600,7 @@
       <c r="Q67" t="n">
         <v>5</v>
       </c>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5605,6 +5676,7 @@
       <c r="Q68" t="n">
         <v>5</v>
       </c>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5680,6 +5752,7 @@
       <c r="Q69" t="n">
         <v>5</v>
       </c>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5755,6 +5828,7 @@
       <c r="Q70" t="n">
         <v>5</v>
       </c>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5830,6 +5904,7 @@
       <c r="Q71" t="n">
         <v>5</v>
       </c>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5905,6 +5980,7 @@
       <c r="Q72" t="n">
         <v>5</v>
       </c>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5980,6 +6056,7 @@
       <c r="Q73" t="n">
         <v>5</v>
       </c>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6055,6 +6132,7 @@
       <c r="Q74" t="n">
         <v>5</v>
       </c>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6130,6 +6208,7 @@
       <c r="Q75" t="n">
         <v>5</v>
       </c>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6205,6 +6284,7 @@
       <c r="Q76" t="n">
         <v>5</v>
       </c>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6280,6 +6360,7 @@
       <c r="Q77" t="n">
         <v>5</v>
       </c>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6355,6 +6436,7 @@
       <c r="Q78" t="n">
         <v>5</v>
       </c>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6430,6 +6512,7 @@
       <c r="Q79" t="n">
         <v>5</v>
       </c>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6505,6 +6588,7 @@
       <c r="Q80" t="n">
         <v>5</v>
       </c>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6580,6 +6664,7 @@
       <c r="Q81" t="n">
         <v>5</v>
       </c>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6655,6 +6740,7 @@
       <c r="Q82" t="n">
         <v>5</v>
       </c>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6730,6 +6816,7 @@
       <c r="Q83" t="n">
         <v>5</v>
       </c>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6805,6 +6892,7 @@
       <c r="Q84" t="n">
         <v>5</v>
       </c>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6880,6 +6968,7 @@
       <c r="Q85" t="n">
         <v>5</v>
       </c>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6955,6 +7044,7 @@
       <c r="Q86" t="n">
         <v>5</v>
       </c>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7032,6 +7122,7 @@
       <c r="Q87" t="n">
         <v>5</v>
       </c>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7107,6 +7198,7 @@
       <c r="Q88" t="n">
         <v>5</v>
       </c>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7182,6 +7274,7 @@
       <c r="Q89" t="n">
         <v>5</v>
       </c>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7257,6 +7350,7 @@
       <c r="Q90" t="n">
         <v>5</v>
       </c>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7332,6 +7426,7 @@
       <c r="Q91" t="n">
         <v>5</v>
       </c>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7407,6 +7502,7 @@
       <c r="Q92" t="n">
         <v>5</v>
       </c>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7482,6 +7578,7 @@
       <c r="Q93" t="n">
         <v>5</v>
       </c>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7557,6 +7654,7 @@
       <c r="Q94" t="n">
         <v>5</v>
       </c>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7632,6 +7730,7 @@
       <c r="Q95" t="n">
         <v>5</v>
       </c>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7707,6 +7806,7 @@
       <c r="Q96" t="n">
         <v>5</v>
       </c>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7782,6 +7882,7 @@
       <c r="Q97" t="n">
         <v>5</v>
       </c>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7857,6 +7958,7 @@
       <c r="Q98" t="n">
         <v>5</v>
       </c>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7932,6 +8034,7 @@
       <c r="Q99" t="n">
         <v>5</v>
       </c>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8009,6 +8112,7 @@
       <c r="Q100" t="n">
         <v>6</v>
       </c>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8084,6 +8188,7 @@
       <c r="Q101" t="n">
         <v>6</v>
       </c>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8159,6 +8264,7 @@
       <c r="Q102" t="n">
         <v>6</v>
       </c>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8234,6 +8340,7 @@
       <c r="Q103" t="n">
         <v>6</v>
       </c>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8309,6 +8416,7 @@
       <c r="Q104" t="n">
         <v>6</v>
       </c>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8386,6 +8494,7 @@
       <c r="Q105" t="n">
         <v>6</v>
       </c>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8463,6 +8572,7 @@
       <c r="Q106" t="n">
         <v>6</v>
       </c>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8515,7 +8625,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>{"placeholder": "List medications", "validation": {"min": 1, "max": 500}}</t>
+          <t>{"place_holder": "List medications", "validation": {"min": 1, "max": 500}}</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8540,6 +8650,7 @@
       <c r="Q107" t="n">
         <v>6</v>
       </c>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8617,6 +8728,7 @@
       <c r="Q108" t="n">
         <v>6</v>
       </c>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8669,7 +8781,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>{"input": [{"type": "number_input", "metadata": {"placeholder": "Enter systolic (top) number", "validation": {"min": 50, "max": 300}}, "ordinal": 1}, {"type": "number_input", "metadata": {"placeholder": "Enter diastolic (bottom) number", "validation": {"min": 40, "max": 200}}, "ordinal": 2}], "can_skip": true}</t>
+          <t>{"input": [{"type": "number_input", "metadata": {"place_holder": "Enter systolic (top) number", "validation": {"min": 50, "max": 300}}, "ordinal": 1}, {"type": "number_input", "metadata": {"place_holder": "Enter diastolic (bottom) number", "validation": {"min": 40, "max": 200}}, "ordinal": 2}], "can_skip": true}</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8694,6 +8806,7 @@
       <c r="Q109" t="n">
         <v>6</v>
       </c>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8771,6 +8884,7 @@
       <c r="Q110" t="n">
         <v>7</v>
       </c>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8848,6 +8962,7 @@
       <c r="Q111" t="n">
         <v>1</v>
       </c>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8925,6 +9040,7 @@
       <c r="Q112" t="n">
         <v>1</v>
       </c>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8977,7 +9093,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your current occupation", "validation": {"min": 1, "max": 1000}}</t>
+          <t>{"place_holder": "Enter your current occupation", "validation": {"min": 1, "max": 1000}}</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -9002,6 +9118,7 @@
       <c r="Q113" t="n">
         <v>1</v>
       </c>
+      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9079,6 +9196,7 @@
       <c r="Q114" t="n">
         <v>1</v>
       </c>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9156,6 +9274,7 @@
       <c r="Q115" t="n">
         <v>1</v>
       </c>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9233,6 +9352,7 @@
       <c r="Q116" t="n">
         <v>1</v>
       </c>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9310,6 +9430,7 @@
       <c r="Q117" t="n">
         <v>1</v>
       </c>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9387,6 +9508,7 @@
       <c r="Q118" t="n">
         <v>1</v>
       </c>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9437,7 +9559,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter other health goal", "validation": {"min": 1, "max": 1000}}</t>
+          <t>{"place_holder": "Enter other health goal", "validation": {"min": 1, "max": 1000}}</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9462,6 +9584,7 @@
       <c r="Q119" t="n">
         <v>1</v>
       </c>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9539,6 +9662,7 @@
       <c r="Q120" t="n">
         <v>1</v>
       </c>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9589,7 +9713,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your answer"}</t>
+          <t>{"place_holder": "Enter your answer"}</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9614,6 +9738,7 @@
       <c r="Q121" t="n">
         <v>1</v>
       </c>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9691,6 +9816,7 @@
       <c r="Q122" t="n">
         <v>1</v>
       </c>
+      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9741,7 +9867,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your answer"}</t>
+          <t>{"place_holder": "Enter your answer"}</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9766,6 +9892,7 @@
       <c r="Q123" t="n">
         <v>1</v>
       </c>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9843,6 +9970,7 @@
       <c r="Q124" t="n">
         <v>8</v>
       </c>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9920,6 +10048,7 @@
       <c r="Q125" t="n">
         <v>8</v>
       </c>
+      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9995,6 +10124,7 @@
       <c r="Q126" t="n">
         <v>8</v>
       </c>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -10070,6 +10200,7 @@
       <c r="Q127" t="n">
         <v>8</v>
       </c>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -10147,6 +10278,7 @@
       <c r="Q128" t="n">
         <v>8</v>
       </c>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10224,6 +10356,7 @@
       <c r="Q129" t="n">
         <v>8</v>
       </c>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10274,7 +10407,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>{"placeholder": "times a week", "validation": {"min": 0, "max": 1000}}</t>
+          <t>{"place_holder": "times a week", "validation": {"min": 0, "max": 1000}}</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10299,6 +10432,7 @@
       <c r="Q130" t="n">
         <v>8</v>
       </c>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10349,7 +10483,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your number", "validation": {"min": 0, "max": 150}}</t>
+          <t>{"place_holder": "Enter your number", "validation": {"min": 0, "max": 150}}</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10370,6 +10504,7 @@
       <c r="Q131" t="n">
         <v>8</v>
       </c>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10441,6 +10576,7 @@
       <c r="Q132" t="n">
         <v>8</v>
       </c>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10491,7 +10627,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your number", "validation": {"min": 0, "max": 1000}}</t>
+          <t>{"place_holder": "Enter your number", "validation": {"min": 0, "max": 1000}}</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10512,6 +10648,7 @@
       <c r="Q133" t="n">
         <v>8</v>
       </c>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10562,7 +10699,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>{"placeholder": "years ago", "validation": {"min": 0, "max": 150}}</t>
+          <t>{"place_holder": "years ago", "validation": {"min": 0, "max": 150}}</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10587,6 +10724,7 @@
       <c r="Q134" t="n">
         <v>8</v>
       </c>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10664,6 +10802,7 @@
       <c r="Q135" t="n">
         <v>8</v>
       </c>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10739,6 +10878,7 @@
       <c r="Q136" t="n">
         <v>8</v>
       </c>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10816,6 +10956,7 @@
       <c r="Q137" t="n">
         <v>8</v>
       </c>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10891,6 +11032,7 @@
       <c r="Q138" t="n">
         <v>8</v>
       </c>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10968,6 +11110,7 @@
       <c r="Q139" t="n">
         <v>8</v>
       </c>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -11043,6 +11186,7 @@
       <c r="Q140" t="n">
         <v>8</v>
       </c>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -11120,6 +11264,7 @@
       <c r="Q141" t="n">
         <v>8</v>
       </c>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -11195,6 +11340,7 @@
       <c r="Q142" t="n">
         <v>8</v>
       </c>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -11270,6 +11416,7 @@
       <c r="Q143" t="n">
         <v>8</v>
       </c>
+      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11345,6 +11492,7 @@
       <c r="Q144" t="n">
         <v>8</v>
       </c>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11420,6 +11568,7 @@
       <c r="Q145" t="n">
         <v>8</v>
       </c>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11495,6 +11644,7 @@
       <c r="Q146" t="n">
         <v>8</v>
       </c>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11570,6 +11720,7 @@
       <c r="Q147" t="n">
         <v>8</v>
       </c>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11645,6 +11796,7 @@
       <c r="Q148" t="n">
         <v>8</v>
       </c>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11720,6 +11872,7 @@
       <c r="Q149" t="n">
         <v>8</v>
       </c>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11795,6 +11948,7 @@
       <c r="Q150" t="n">
         <v>8</v>
       </c>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11870,6 +12024,7 @@
       <c r="Q151" t="n">
         <v>8</v>
       </c>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11945,6 +12100,7 @@
       <c r="Q152" t="n">
         <v>8</v>
       </c>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -12020,6 +12176,7 @@
       <c r="Q153" t="n">
         <v>8</v>
       </c>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -12095,6 +12252,7 @@
       <c r="Q154" t="n">
         <v>8</v>
       </c>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -12170,6 +12328,7 @@
       <c r="Q155" t="n">
         <v>8</v>
       </c>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -12247,6 +12406,7 @@
       <c r="Q156" t="n">
         <v>8</v>
       </c>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -12324,6 +12484,7 @@
       <c r="Q157" t="n">
         <v>8</v>
       </c>
+      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12376,7 +12537,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your number", "validation": {"min": 0, "max": 25}}</t>
+          <t>{"place_holder": "Enter your number", "validation": {"min": 0, "max": 25}}</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -12401,6 +12562,7 @@
       <c r="Q158" t="n">
         <v>8</v>
       </c>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12478,6 +12640,7 @@
       <c r="Q159" t="n">
         <v>8</v>
       </c>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12555,6 +12718,7 @@
       <c r="Q160" t="n">
         <v>8</v>
       </c>
+      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12632,6 +12796,7 @@
       <c r="Q161" t="n">
         <v>8</v>
       </c>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12709,6 +12874,7 @@
       <c r="Q162" t="n">
         <v>8</v>
       </c>
+      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12786,6 +12952,7 @@
       <c r="Q163" t="n">
         <v>8</v>
       </c>
+      <c r="R163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12863,6 +13030,7 @@
       <c r="Q164" t="n">
         <v>8</v>
       </c>
+      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12940,6 +13108,7 @@
       <c r="Q165" t="n">
         <v>8</v>
       </c>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -13017,6 +13186,7 @@
       <c r="Q166" t="n">
         <v>8</v>
       </c>
+      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -13090,6 +13260,7 @@
       <c r="Q167" t="n">
         <v>1</v>
       </c>
+      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -13163,6 +13334,7 @@
       <c r="Q168" t="n">
         <v>1</v>
       </c>
+      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -13236,6 +13408,7 @@
       <c r="Q169" t="n">
         <v>1</v>
       </c>
+      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -13288,7 +13461,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>{"placeholder": "Enter your number", "validation": {"min": 1, "max": 100}}</t>
+          <t>{"place_holder": "Enter your number", "validation": {"min": 1, "max": 100}}</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -13309,6 +13482,7 @@
       <c r="Q170" t="n">
         <v>1</v>
       </c>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -13382,6 +13556,7 @@
       <c r="Q171" t="n">
         <v>1</v>
       </c>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -13455,6 +13630,7 @@
       <c r="Q172" t="n">
         <v>1</v>
       </c>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13528,6 +13704,7 @@
       <c r="Q173" t="n">
         <v>1</v>
       </c>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13601,6 +13778,7 @@
       <c r="Q174" t="n">
         <v>1</v>
       </c>
+      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13674,6 +13852,7 @@
       <c r="Q175" t="n">
         <v>1</v>
       </c>
+      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13747,6 +13926,7 @@
       <c r="Q176" t="n">
         <v>1</v>
       </c>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13820,6 +14000,7 @@
       <c r="Q177" t="n">
         <v>1</v>
       </c>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13893,6 +14074,7 @@
       <c r="Q178" t="n">
         <v>1</v>
       </c>
+      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13966,6 +14148,7 @@
       <c r="Q179" t="n">
         <v>1</v>
       </c>
+      <c r="R179" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
